--- a/event_feedback_forms/024_digital_interactive_experience_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/024_digital_interactive_experience_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_11.1,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 11.1, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'webinar'}</t>
+          <t>webinar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'webinar'}</t>
+          <t>webinar</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'workshop'}</t>
+          <t>workshop</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'conference'}</t>
+          <t>conference</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'training'}</t>
+          <t>training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'training'}</t>
+          <t>training</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_16.1,_'label':_'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 16.1, 'label': 'seminar'}</t>
+          <t>seminar</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': 'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_17.1,_'label':_'not_now'}</t>
+          <t>not_now</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 17.1, 'label': 'not now'}</t>
+          <t>not now</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': '1-2'}</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': '3-4'}</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'5-6'}</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': '5-6'}</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'7-8'}</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': '7-8'}</t>
+          <t>7-8</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_21.1,_'label':_'9-10'}</t>
+          <t>9-10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 21.1, 'label': '9-10'}</t>
+          <t>9-10</t>
         </is>
       </c>
     </row>
